--- a/mvvmのダメなところと理想像.xlsx
+++ b/mvvmのダメなところと理想像.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15309" activeTab="1"/>
+    <workbookView windowWidth="28345" windowHeight="14700"/>
   </bookViews>
   <sheets>
     <sheet name="MVVMの問題" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
   <si>
     <t>MVVMは今一つの感じがぬぐえなかったが、その理由が分かった。</t>
   </si>
@@ -28,6 +28,30 @@
   </si>
   <si>
     <t>本来はアトミックな処理が終了したら、その処理内で更新されたプロパティの更新通知がVMに行くようにしなければならない。</t>
+  </si>
+  <si>
+    <t>VMとMの関係が事実上無法地帯</t>
+  </si>
+  <si>
+    <t>この関係について、MSは標準的なアーキテクチャを提示しておらず、アプリ開発者に責任が丸投げされている。</t>
+  </si>
+  <si>
+    <t>とりあえず、以下のようにする。</t>
+  </si>
+  <si>
+    <t>VMからMへの要求は、Mの用意するキューに積むだけ。VMがMの処理が終わるのを待ったりしない。</t>
+  </si>
+  <si>
+    <t>Mのメイン処理は、UIスレッドとは別のスレッドで処理する。Mは子のスレッドで、キューに追加された要求を取り出し、処理を行う。</t>
+  </si>
+  <si>
+    <t>Mが処理を終えたら、この処理で更新されたデータモデルの内容を、VMに通知する。</t>
+  </si>
+  <si>
+    <t>VMがMからのデータモデルの更新内容を受け取るため、VMの初期化処理で、Mに自分自身をリスナー登録する。</t>
+  </si>
+  <si>
+    <t>リスナー登録時は、Mの開陳するデータモデル内の項目名を購読対象として登録する。</t>
   </si>
   <si>
     <t>Modelについて</t>
@@ -185,10 +209,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -206,8 +230,44 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -215,73 +275,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,17 +297,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -320,14 +352,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -337,14 +361,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -359,25 +383,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,108 +557,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -498,48 +564,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -550,17 +574,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -588,6 +601,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -599,21 +627,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -650,6 +663,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -658,145 +682,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1155,8 +1179,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:C5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.25" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="B2:C18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.25" outlineLevelCol="2"/>
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" t="s">
@@ -1176,6 +1200,46 @@
     <row r="5" spans="3:3">
       <c r="C5" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3">
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1193,216 +1257,216 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="3:7">
       <c r="C6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="3:3">
       <c r="C14" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="3:7">
       <c r="C20" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="3:3">
       <c r="C27" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="3:3">
       <c r="C32" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="3:3">
       <c r="C34" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="3:3">
       <c r="C37" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="4:4">
       <c r="D38" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="3:3">
       <c r="C39" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="4:4">
       <c r="D40" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="4:4">
       <c r="D41" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="3:3">
       <c r="C42" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="4:4">
       <c r="D43" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="3:3">
       <c r="C58" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="3:3">
       <c r="C59" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="3:3">
       <c r="C63" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="3:3">
       <c r="C64" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="4:4">
       <c r="D65" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="4:4">
       <c r="D66" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="5:5">
       <c r="E67" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="72" spans="3:3">
       <c r="C72" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1420,41 +1484,41 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="4:6">
       <c r="D4" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="4:6">
       <c r="D5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="4:6">
       <c r="D6" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/mvvmのダメなところと理想像.xlsx
+++ b/mvvmのダメなところと理想像.xlsx
@@ -4,19 +4,24 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28345" windowHeight="14700"/>
+    <workbookView windowWidth="28345" windowHeight="14700" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="MVVMの問題" sheetId="1" r:id="rId1"/>
     <sheet name="本来あるべき姿" sheetId="2" r:id="rId2"/>
     <sheet name="PropertyTree" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet2!$C$14:$H$43</definedName>
+  </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="104">
   <si>
     <t>MVVMは今一つの感じがぬぐえなかったが、その理由が分かった。</t>
   </si>
@@ -202,6 +207,132 @@
   </si>
   <si>
     <t>(2) VFE</t>
+  </si>
+  <si>
+    <t>geminiによると、ウィンドウのサイズ、状態（最大化など）を永続化する場合、VMにサイズ、状態のバインディングプロパティを用意し、twowayでバインドする。</t>
+  </si>
+  <si>
+    <t>ただ、実際には面倒なだけに思える。windowに直接アクセスした方が手っ取り早い。アプリ実行中に、ウィンドウのサイズなどがVM側にも連携されても何の意味もないということもある。</t>
+  </si>
+  <si>
+    <t>tabが一つ追加された場合</t>
+  </si>
+  <si>
+    <t>末尾に追加する。</t>
+  </si>
+  <si>
+    <t>今回追加されたものを選択状態にする</t>
+  </si>
+  <si>
+    <t>tabが複数追加された場合</t>
+  </si>
+  <si>
+    <t>今回追加されたもののうち、先頭のものを選択状態にする</t>
+  </si>
+  <si>
+    <t>末尾のタブが選択されている状態で、そのタブが削除された場合</t>
+  </si>
+  <si>
+    <t>一つ手前のタブを選択する</t>
+  </si>
+  <si>
+    <t>tabが一つ削除され、そのタブが選択されていた場合</t>
+  </si>
+  <si>
+    <t>次のものを選択する</t>
+  </si>
+  <si>
+    <t>現状</t>
+  </si>
+  <si>
+    <t>結果</t>
+  </si>
+  <si>
+    <t>要素</t>
+  </si>
+  <si>
+    <t>選択</t>
+  </si>
+  <si>
+    <t>add</t>
+  </si>
+  <si>
+    <t>delete</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>[a]</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>[a, b]</t>
+  </si>
+  <si>
+    <t>[a, b, c]</t>
+  </si>
+  <si>
+    <t>[b]</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>[c]</t>
+  </si>
+  <si>
+    <t>[a, c]</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>[b, c]</t>
+  </si>
+  <si>
+    <t>非選択状態のタブを削除した場合、選択状態は変わらない。</t>
+  </si>
+  <si>
+    <t>選択状態のタブを削除した場合、</t>
+  </si>
+  <si>
+    <t>右隣にタブがあった場合、そのタブが選択される。</t>
+  </si>
+  <si>
+    <t>右隣にタブがなかった場合、</t>
+  </si>
+  <si>
+    <t>左隣にタブがあった場合、そのタブが選択される。</t>
+  </si>
+  <si>
+    <t>左隣にタブがなかった場合、すなわち一つしかなかったタブを削除した場合、タブが一つもない状態になるので、選択状態のタブという概念がなくなる。</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>↑</t>
+  </si>
+  <si>
+    <t>→</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>D</t>
   </si>
 </sst>
 </file>
@@ -209,10 +340,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -230,20 +361,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -253,61 +370,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,9 +392,62 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -361,7 +477,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +505,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -383,73 +514,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.15"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -461,24 +694,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -489,91 +704,76 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="14">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -592,25 +792,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -631,17 +822,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,6 +849,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -682,150 +882,168 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1274,7 +1492,7 @@
       <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="1"/>
+      <c r="G6" s="7"/>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
@@ -1320,7 +1538,7 @@
       <c r="C20" t="s">
         <v>24</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1526,4 +1744,869 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="13.25" outlineLevelRow="2" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C2:O83"/>
+  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="13.25"/>
+  <cols>
+    <col min="3" max="7" width="7.95495495495495" customWidth="1"/>
+    <col min="8" max="8" width="5.48648648648649" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="10:10">
+      <c r="J2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="11:11">
+      <c r="K3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="11:11">
+      <c r="K4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="10:10">
+      <c r="J5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="11:11">
+      <c r="K6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="11:11">
+      <c r="K7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="10:10">
+      <c r="J8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="11:11">
+      <c r="K9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="10:10">
+      <c r="J10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="11:11">
+      <c r="K11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8">
+      <c r="C13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="3:8">
+      <c r="C14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="3:8">
+      <c r="C15" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="3:8">
+      <c r="C16" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="3:8">
+      <c r="C17" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="3:8">
+      <c r="C18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="3:8">
+      <c r="C19" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="3:8">
+      <c r="C20" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="3:8">
+      <c r="C21" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="3:8">
+      <c r="C22" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="3:8">
+      <c r="C23" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" spans="3:8">
+      <c r="C24" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="3:8">
+      <c r="C25" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="3:8">
+      <c r="C26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="3:8">
+      <c r="C27" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="3:8">
+      <c r="C28" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="3:8">
+      <c r="C29" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" spans="3:8">
+      <c r="C30" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" spans="3:8">
+      <c r="C31" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="3:8">
+      <c r="C32" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="3:8">
+      <c r="C33" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="3:8">
+      <c r="C34" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" spans="3:8">
+      <c r="C35" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" spans="3:8">
+      <c r="C36" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="3:8">
+      <c r="C37" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="3:8">
+      <c r="C38" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" spans="3:8">
+      <c r="C39" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40" spans="3:6">
+      <c r="C40" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="3:6">
+      <c r="C41" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="3:6">
+      <c r="C42" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F42" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="3:5">
+      <c r="C43" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3">
+      <c r="C50" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="52" spans="3:3">
+      <c r="C52" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="53" spans="4:4">
+      <c r="D53" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="54" spans="4:4">
+      <c r="D54" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="55" spans="5:5">
+      <c r="E55" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" spans="5:5">
+      <c r="E56" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="65" spans="9:14">
+      <c r="I65" t="s">
+        <v>97</v>
+      </c>
+      <c r="J65" t="s">
+        <v>98</v>
+      </c>
+      <c r="K65" t="s">
+        <v>99</v>
+      </c>
+      <c r="M65" t="s">
+        <v>97</v>
+      </c>
+      <c r="N65" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="66" spans="9:13">
+      <c r="I66" t="s">
+        <v>100</v>
+      </c>
+      <c r="L66" t="s">
+        <v>101</v>
+      </c>
+      <c r="M66" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="9:11">
+      <c r="I67" t="s">
+        <v>80</v>
+      </c>
+      <c r="J67" t="s">
+        <v>102</v>
+      </c>
+      <c r="K67" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70" spans="9:14">
+      <c r="I70" t="s">
+        <v>97</v>
+      </c>
+      <c r="J70" t="s">
+        <v>98</v>
+      </c>
+      <c r="K70" t="s">
+        <v>99</v>
+      </c>
+      <c r="M70" t="s">
+        <v>97</v>
+      </c>
+      <c r="N70" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="71" spans="10:14">
+      <c r="J71" t="s">
+        <v>100</v>
+      </c>
+      <c r="L71" t="s">
+        <v>101</v>
+      </c>
+      <c r="N71" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="9:11">
+      <c r="I72" t="s">
+        <v>80</v>
+      </c>
+      <c r="J72" t="s">
+        <v>102</v>
+      </c>
+      <c r="K72" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76" spans="9:13">
+      <c r="I76" t="s">
+        <v>97</v>
+      </c>
+      <c r="J76" t="s">
+        <v>98</v>
+      </c>
+      <c r="K76" t="s">
+        <v>99</v>
+      </c>
+      <c r="M76" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="77" spans="9:13">
+      <c r="I77" t="s">
+        <v>100</v>
+      </c>
+      <c r="L77" t="s">
+        <v>101</v>
+      </c>
+      <c r="M77" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78" spans="9:11">
+      <c r="I78" t="s">
+        <v>102</v>
+      </c>
+      <c r="J78" t="s">
+        <v>102</v>
+      </c>
+      <c r="K78" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="9:15">
+      <c r="I81" t="s">
+        <v>97</v>
+      </c>
+      <c r="J81" t="s">
+        <v>98</v>
+      </c>
+      <c r="K81" t="s">
+        <v>99</v>
+      </c>
+      <c r="L81" t="s">
+        <v>103</v>
+      </c>
+      <c r="N81" t="s">
+        <v>98</v>
+      </c>
+      <c r="O81" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="82" spans="9:14">
+      <c r="I82" t="s">
+        <v>100</v>
+      </c>
+      <c r="M82" t="s">
+        <v>101</v>
+      </c>
+      <c r="N82" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83" spans="9:12">
+      <c r="I83" t="s">
+        <v>102</v>
+      </c>
+      <c r="J83" t="s">
+        <v>80</v>
+      </c>
+      <c r="K83" t="s">
+        <v>80</v>
+      </c>
+      <c r="L83" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="C14:H43">
+    <extLst/>
+  </autoFilter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>